--- a/1_Data/Zhao_2026_PsychonBullRev/Exp2/Codebook_Zhao_2026_PsychonBullRev_Exp2_Clean.xlsx
+++ b/1_Data/Zhao_2026_PsychonBullRev/Exp2/Codebook_Zhao_2026_PsychonBullRev_Exp2_Clean.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +420,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Variable_description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Variable_value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Variable_category</t>
         </is>
@@ -444,19 +457,19 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Participant ID as used by the authors in the shared OSF files (subj_idx; ids of participants excluded by the authors before analysis are absent from the shared files)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1; 2; 3; 4; 5; 6; 7; 8; 9; 10; 11; 12; 13; 15; 16; 17; 18; 19; 20; 21; 22; 23; 24; 25; 26; 27; 28; 29; 30; 31; 32; 33; 34; 35; 36; 37; 38; 39; 40; 41; 42; 43; 44; 45; 46; 47; 48</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Participant ID as used by the authors (file-name prefix in the original PsychoPy data; identical to subj_idx in the authors' OSF analysis file). All participants with data are included including the 2 participants (ids 14, 49) excluded by the authors for below-chance accuracy.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Number (participant id)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Numerical</t>
         </is>
       </c>
     </row>
@@ -466,12 +479,12 @@
           <t>Task</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Task type: shape-label matching with self-relevant identity associations (self-matching)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Task type: self-matching = shape-label matching with self-referential identity associations (Sui et al., 2012 paradigm)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>self-matching</t>
         </is>
@@ -485,17 +498,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trial type: Matching = presented shape-label pair consistent with the learned association; Nonmatching = inconsistent pair</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Matching; Nonmatching</t>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Trial phase: practice = criterion practice block; formal = main experiment. Practice trials are retained (flagged here) and are not part of the authors' analyses.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>practice; formal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,17 +520,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Shape-side stimulus. Value 'missing': geometric shape identity binding was counterbalanced across participants and the individual shape geometry was not recorded in the shared analysis files</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>missing (see description)</t>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Block number 1-6 of the main experiment (60 trials per block; a self-paced rest screen followed trials 60, 120, 180, 240 and 300). NA for practice trials, which formed a single criterion-based sequence without block structure.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1; 2; 3; 4; 5; 6; NA (practice trials)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -529,39 +542,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Identity associated with the shape, as coded by the authors (English code words from the OSF data dictionary; on-screen label language/wording to be confirmed with the authors)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>friend; general self; stranger</t>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Trial number: 1-60 within each block for formal trials; 1-n within the practice sequence for practice trials.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Number (trial number)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Numerical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>English label of the shape-associated identity (same as Origin for these author code words)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>friend; general self; stranger</t>
+          <t>Matching</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Trial type: Matching = the presented shape-label pair was consistent with the learned shape-identity association; Nonmatching = re-paired (inconsistent) combination.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Matching; Nonmatching</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,17 +586,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Standardized identity category (Self / Close / Stranger). Both 'true self' and 'general self' map to Self; 'friend' to Close; 'stranger' to Stranger</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Close; Self; Stranger</t>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Shape stimulus as presented, given as the stimulus image file used by the authors (all images 300 x 300 px; rectangle.png renders a square of 214 x 213 px, matching the 'circle, square, triangle' wording of the article). The shape-identity binding was counterbalanced across participants (conditions 1-6) and is recorded per trial in this column.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rectangle.png; circle.png; triangle.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +608,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Label-side stimulus word. Value 'missing': the exact label word was not recorded in the shared analysis files (on-screen language/wording to be confirmed with the authors)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>missing (see description)</t>
+          <t>Shape_Origin_Identity</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>The authors' numeric code for the identity bound to the presented shape, verbatim from the original data (Experiment 2 codes: 1 = general self (一般我), 2 = friend (朋友), 3 = stranger (陌生人)). Code meanings differ between the three experiments. Analyses should use Shape_Standardized_Identity, or Shape_English_Identity when the two self aspects must be kept apart.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1; 3; 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,17 +630,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Identity of the presented label word. On Matching trials it equals the shape identity (by definition of a matching pair); on Nonmatching trials the paired label identity was not recorded -&gt; 'missing'</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>friend; general self; stranger; missing</t>
+          <t>Shape_English_Identity</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>English identity associated with the presented shape (general self; friend; stranger).</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>general self; stranger; friend</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,17 +652,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>English label of the presented label identity (same rule as Origin)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>friend; general self; stranger; missing</t>
+          <t>Shape_Standardized_Identity</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Standardized identity category of the shape (database 6-category vocabulary: true self and general self -&gt; Self, friend -&gt; Close, stranger -&gt; Stranger). NOTE: in Experiments 1 and 3 the two self aspects collapse onto Self, so this column alone cannot identify a matching pair; compare Shape_English_Identity with Label_English_Identity instead.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Self; Stranger; Close</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -661,17 +674,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Standardized category of the presented label identity (same rule as Origin; 'missing' when unknown)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Close; Self; Stranger; missing</t>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Label stimulus word presented on screen, in the original Chinese wording.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>一般我; 陌生人; 朋友</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -683,17 +696,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Semantic response: 1 = participant pressed the key assigned to 'match'; 0 = key assigned to 'non-match'. Physical keys (Z/M) were counterbalanced across participants and not recorded</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0 (non-match key); 1 (match key)</t>
+          <t>Label_Origin_Identity</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Identity of the presented label word, verbatim from the original data (original Chinese wording). Recorded for every trial, including nonmatching trials (the paired label identity is part of the original trial log).</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>一般我; 陌生人; 朋友</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,64 +718,174 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RT_ms</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Reaction time of the response in milliseconds (author rt column in seconds x 1000; shared files contain only trials with a response and RT &gt;= 200 ms)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Number (ms)</t>
+          <t>Label_English_Identity</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>English translation of the identity of the presented label word.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>general self; stranger; friend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RT_sec</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Reaction time in seconds (author rt column, unmodified)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Number (seconds)</t>
+          <t>Label_Standardized_Identity</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Standardized identity category of the presented label word (Self / Close / Stranger; see the note on Shape_Standardized_Identity).</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Self; Stranger; Close</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CorrResponse</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Correct response key for the trial as defined by the participant's counterbalanced key assignment (z or m; the 'match' and 'non-match' keys were swapped between conditions A and B).</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>m; z</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Key actually pressed by the participant (z or m; only these two keys were recorded). NA = no response within the response window.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>m; z; NA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RT_ms</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Reaction time in milliseconds (original PsychoPy rt in seconds multiplied by 1000, unmodified). All responses are kept, i.e. no RT filtering was applied; NA for no-response trials.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Number (ms)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Reaction time in seconds (original PsychoPy rt column, unmodified); NA for no-response trials.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Number (seconds)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Accuracy: 1 = correct response, 0 = incorrect (wrong match/non-match key within the response window). No-response/too-fast trials were removed by the authors before sharing and are absent; corr column reproduced 100% as (match == response)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0 (incorrect); 1 (correct)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy per database coding: 1 = correct key, 0 = incorrect key (both within the 1100 ms response window), NA = no response. PsychoPy records corr = 0 for no-response trials; those are recoded to NA here. Only z and m were possible responses, so the codes -2/-3/-4 do not occur.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1; 0; NA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Counterbalance</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Counterbalance condition assigned by the programme (author variable 'condition', 12 combinations): the digit gives the shape-identity binding (1 = circle-true self / square-general self / triangle-stranger, 2 = circle-true self / triangle-general self / square-stranger, 3-6 accordingly) and the letter gives the response-key mapping (A: match = z, non-match = m; B: match = m, non-match = z). Research-specific column retained for counterbalancing checks.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4B; 1B; 5A; 2B; 6A; 2A; 4A; 6B; 3A; 1A; 3B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
